--- a/docs/referencia/inventario-fisico-template.xlsx
+++ b/docs/referencia/inventario-fisico-template.xlsx
@@ -8,58 +8,194 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\Negocios\ORVANN\orvann-gestion\docs\referencia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0336D75-3A6C-44C6-B2B8-B8B54A050604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{A06F1F76-043E-4F9E-8749-5E6798438F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896"/>
   </bookViews>
   <sheets>
-    <sheet name="inventario-fisico-template" sheetId="1" r:id="rId1"/>
+    <sheet name="Inventario fisico" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>tipo,producto_base,color,talla,diseno,estampado,cantidad,costo_unit,precio_venta,zona,observacion</t>
-  </si>
-  <si>
-    <t>prenda,Camisa Oversize Peruana,Negro,S,,ninguno,1,37000,75000,A,</t>
-  </si>
-  <si>
-    <t>prenda,Camisa Oversize Peruana,Negro,M,,ninguno,5,37000,75000,A,</t>
-  </si>
-  <si>
-    <t>prenda,Camisa Oversize Peruana,Negro,L,,ninguno,2,37000,75000,A,</t>
-  </si>
-  <si>
-    <t>prenda,Camisa Oversize Peruana,Blanco,M,Pulp Fiction,completo_dtg,3,49000,90000,A,ejemplo estampada</t>
-  </si>
-  <si>
-    <t>prenda,Hoodie Acid Wash,Gris,L,,ninguno,0,120000,190000,B,agotado</t>
-  </si>
-  <si>
-    <t>fragancia,LociÃ³n Amaderada 100ml,,Ãšnica,,,4,35000,70000,D,ejemplo accesorio</t>
-  </si>
-  <si>
-    <t>accesorio,Candela AromÃ¡tica 200g,Negro,Ãšnica,,,6,15000,35000,D,ejemplo</t>
-  </si>
-  <si>
-    <t>accesorio,Llavero MetÃ¡lico ORVANN,,Ãšnica,,,12,3000,10000,E,</t>
-  </si>
-  <si>
-    <t>accesorio,Rascador Vinilos,,Ãšnica,,,3,8000,20000,E,</t>
-  </si>
-  <si>
-    <t>accesorio,Vaporizador PortÃ¡til,,Ãšnica,,,5,45000,90000,E,</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="55">
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Producto_base</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Talla</t>
+  </si>
+  <si>
+    <t>Diseño</t>
+  </si>
+  <si>
+    <t>Cantidad</t>
+  </si>
+  <si>
+    <t>Costo_unit</t>
+  </si>
+  <si>
+    <t>Precio_venta</t>
+  </si>
+  <si>
+    <t>Observación</t>
+  </si>
+  <si>
+    <t>Camisa Oversize Peruana</t>
+  </si>
+  <si>
+    <t>Negro</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Fragancia</t>
+  </si>
+  <si>
+    <t>Loción Versace 100ml</t>
+  </si>
+  <si>
+    <t>Pulp Fiction</t>
+  </si>
+  <si>
+    <t>Estampada espalda completo y bordada frente</t>
+  </si>
+  <si>
+    <t>Accesorio</t>
+  </si>
+  <si>
+    <t>Candela gasolina 100gr</t>
+  </si>
+  <si>
+    <t>Dorada</t>
+  </si>
+  <si>
+    <t>ejemplo</t>
+  </si>
+  <si>
+    <t>Estampado Punto Corazón</t>
+  </si>
+  <si>
+    <t>Bordado Punto Corazón</t>
+  </si>
+  <si>
+    <t>Estampado Completo</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>Prenda</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>Buzo Cuello Redondo Oversized</t>
+  </si>
+  <si>
+    <t>Chompa Capucha</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Chompa básica</t>
+  </si>
+  <si>
+    <t>XXL</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Básico</t>
+  </si>
+  <si>
+    <t>Perla</t>
+  </si>
+  <si>
+    <t>Beige</t>
+  </si>
+  <si>
+    <t>Beige de Leo - Básica</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>Café</t>
+  </si>
+  <si>
+    <t>Café de Leo - Básica</t>
+  </si>
+  <si>
+    <t>Jhon Wick</t>
+  </si>
+  <si>
+    <t>Camisa Boxy fit</t>
+  </si>
+  <si>
+    <t>Camisa Réplica 1.1</t>
+  </si>
+  <si>
+    <t>Camisa Regular Peruana</t>
+  </si>
+  <si>
+    <t>Acid Wash Gris</t>
+  </si>
+  <si>
+    <t>Ver gramaje y si si es Regular</t>
+  </si>
+  <si>
+    <t>Gris</t>
+  </si>
+  <si>
+    <t>Camisa Réplica Y/Out</t>
+  </si>
+  <si>
+    <t>Blanco</t>
+  </si>
+  <si>
+    <t>Kobe Bryant</t>
+  </si>
+  <si>
+    <t>Solo punto corazon</t>
+  </si>
+  <si>
+    <t>Sudadera Bota Recta</t>
+  </si>
+  <si>
+    <t>Jogger Largo</t>
+  </si>
+  <si>
+    <t>Pantaloneta</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -194,8 +330,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -375,8 +519,20 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF356854"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -491,9 +647,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -536,52 +717,75 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="18" fillId="33" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="34" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Bueno" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Cálculo" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Celda de comprobación" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Celda vinculada" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Encabezado 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Encabezado 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Énfasis1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Énfasis2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Énfasis3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Énfasis4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Énfasis5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Énfasis6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Incorrecto" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+  <cellStyles count="43">
+    <cellStyle name="20% - Énfasis1" xfId="20" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis2" xfId="24" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis3" xfId="28" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis4" xfId="32" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis5" xfId="36" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis6" xfId="40" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis1" xfId="21" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis2" xfId="25" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis3" xfId="29" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis4" xfId="33" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis5" xfId="37" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis6" xfId="41" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis1" xfId="22" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis2" xfId="26" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis3" xfId="30" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis4" xfId="34" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis5" xfId="38" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis6" xfId="42" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Bueno" xfId="7" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Cálculo" xfId="12" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Celda de comprobación" xfId="14" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Celda vinculada" xfId="13" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Encabezado 1" xfId="3" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Encabezado 4" xfId="6" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Énfasis1" xfId="19" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Énfasis2" xfId="23" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Énfasis3" xfId="27" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Énfasis4" xfId="31" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Énfasis5" xfId="35" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Énfasis6" xfId="39" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Entrada" xfId="10" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Incorrecto" xfId="8" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
+    <cellStyle name="Neutral" xfId="9" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Notas" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Salida" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Texto de advertencia" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Texto explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Título" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Título 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Notas" xfId="16" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Salida" xfId="11" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Texto de advertencia" xfId="15" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Texto explicativo" xfId="17" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Título" xfId="2" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Título 2" xfId="4" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Título 3" xfId="5" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -891,67 +1095,1497 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="3">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{D5ED1C11-65A3-4A46-8769-E4D776BDF1DE}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;6723c3b8-c28b-42e9-bcd3-3b145394d46f&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:P63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="41.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="5.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J1" s="8">
+        <f>+SUM(J6:J1048576)</f>
+        <v>46</v>
+      </c>
+      <c r="K1" s="8">
+        <f>+SUMPRODUCT($J$6:$J$1048576,K6:K1048576)</f>
+        <v>890000</v>
+      </c>
+      <c r="L1" s="8">
+        <f>+SUMPRODUCT($J$6:$J$1048576,L6:L1048576)</f>
+        <v>4585000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="G2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="K2" s="6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="L2" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="M2" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="O2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" s="5">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="D3" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="7">
+        <v>3</v>
+      </c>
+      <c r="K3" s="7">
+        <v>49000</v>
+      </c>
+      <c r="L3" s="7">
+        <v>120000</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="7">
+        <v>4</v>
+      </c>
+      <c r="K4" s="7">
+        <v>250000</v>
+      </c>
+      <c r="L4" s="7">
+        <v>380000</v>
+      </c>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="7">
+        <v>2</v>
+      </c>
+      <c r="K5" s="7">
+        <v>8000</v>
+      </c>
+      <c r="L5" s="7">
+        <v>20000</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="8">
+        <v>2</v>
+      </c>
+      <c r="K6" s="8">
+        <v>90000</v>
+      </c>
+      <c r="L6" s="8">
+        <v>180000</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="8">
+        <v>1</v>
+      </c>
+      <c r="L7" s="8">
+        <v>120000</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="8">
+        <v>2</v>
+      </c>
+      <c r="L8" s="8">
+        <v>120000</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="8">
+        <v>1</v>
+      </c>
+      <c r="K9" s="8">
+        <v>90000</v>
+      </c>
+      <c r="L9" s="8">
+        <v>180000</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="8">
+        <v>1</v>
+      </c>
+      <c r="L10" s="8">
+        <v>120000</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" s="8">
+        <v>1</v>
+      </c>
+      <c r="L11" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="8">
+        <v>1</v>
+      </c>
+      <c r="L12" s="8">
+        <v>120000</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="8">
+        <v>1</v>
+      </c>
+      <c r="L13" s="8">
+        <v>120000</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="8">
+        <v>1</v>
+      </c>
+      <c r="L14" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="8">
+        <v>1</v>
+      </c>
+      <c r="L15" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="8">
+        <v>2</v>
+      </c>
+      <c r="L16" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="8">
+        <v>2</v>
+      </c>
+      <c r="L17" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="8">
+        <v>1</v>
+      </c>
+      <c r="L18" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="8">
+        <v>1</v>
+      </c>
+      <c r="K19" s="8">
+        <v>54000</v>
+      </c>
+      <c r="L19" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="8">
+        <v>2</v>
+      </c>
+      <c r="K20" s="8">
+        <v>54000</v>
+      </c>
+      <c r="L20" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="8">
+        <v>1</v>
+      </c>
+      <c r="K21" s="8">
+        <v>36000</v>
+      </c>
+      <c r="L21" s="8">
+        <v>85000</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="8">
+        <v>1</v>
+      </c>
+      <c r="K22" s="8">
+        <v>36000</v>
+      </c>
+      <c r="L22" s="8">
+        <v>85000</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="8">
+        <v>2</v>
+      </c>
+      <c r="K23" s="8">
+        <v>36000</v>
+      </c>
+      <c r="L23" s="8">
+        <v>85000</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="8">
+        <v>2</v>
+      </c>
+      <c r="K24" s="8">
+        <v>36000</v>
+      </c>
+      <c r="L24" s="8">
+        <v>85000</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="8">
+        <v>1</v>
+      </c>
+      <c r="K25" s="8">
+        <v>37000</v>
+      </c>
+      <c r="L25" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="8">
+        <v>1</v>
+      </c>
+      <c r="K26" s="8">
+        <v>37000</v>
+      </c>
+      <c r="L26" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="8">
+        <v>1</v>
+      </c>
+      <c r="K27" s="8">
+        <v>60000</v>
+      </c>
+      <c r="L27" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" s="8">
+        <v>1</v>
+      </c>
+      <c r="L28" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="8">
+        <v>1</v>
+      </c>
+      <c r="L29" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="8">
+        <v>1</v>
+      </c>
+      <c r="L30" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" s="8">
+        <v>1</v>
+      </c>
+      <c r="L31" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J32" s="8">
+        <v>1</v>
+      </c>
+      <c r="L32" s="8">
+        <v>120000</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J33" s="8">
+        <v>2</v>
+      </c>
+      <c r="L33" s="8">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J34" s="8">
+        <v>1</v>
+      </c>
+      <c r="L34" s="8">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J35" s="8">
+        <v>1</v>
+      </c>
+      <c r="L35" s="8">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J36" s="8">
+        <v>1</v>
+      </c>
+      <c r="L36" s="8">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J37" s="8">
+        <v>1</v>
+      </c>
+      <c r="L37" s="8">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J38" s="8">
+        <v>1</v>
+      </c>
+      <c r="L38" s="8">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J39" s="8">
+        <v>1</v>
+      </c>
+      <c r="L39" s="8">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J40" s="8">
+        <v>1</v>
+      </c>
+      <c r="L40" s="8">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J41" s="8">
+        <v>1</v>
+      </c>
+      <c r="L41" s="8">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J42" s="8">
+        <v>1</v>
+      </c>
+      <c r="K42" s="8">
+        <v>54000</v>
+      </c>
+      <c r="L42" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J43" s="8">
+        <v>1</v>
+      </c>
+      <c r="K43" s="8">
+        <v>54000</v>
+      </c>
+      <c r="L43" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/referencia/inventario-fisico-template.xlsx
+++ b/docs/referencia/inventario-fisico-template.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,19 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\Negocios\ORVANN\orvann-gestion\docs\referencia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{A06F1F76-043E-4F9E-8749-5E6798438F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98942CD-A6B2-40F9-AD52-138F6841EAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventario fisico" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="63">
   <si>
     <t>Tipo</t>
   </si>
@@ -185,15 +197,39 @@
   </si>
   <si>
     <t>Pantaloneta</t>
+  </si>
+  <si>
+    <t>Chaqueta Cortavientos</t>
+  </si>
+  <si>
+    <t>Gris Claro/Negro</t>
+  </si>
+  <si>
+    <t>Gris Oscuro</t>
+  </si>
+  <si>
+    <t>Gris Claro</t>
+  </si>
+  <si>
+    <t>Willie Colón</t>
+  </si>
+  <si>
+    <t>Eminem</t>
+  </si>
+  <si>
+    <t>220gr</t>
+  </si>
+  <si>
+    <t>Diomedez</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -732,13 +768,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="18" fillId="33" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="33" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="34" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1118,16 +1154,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P63"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -1141,15 +1177,15 @@
     <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J1" s="8">
         <f>+SUM(J6:J1048576)</f>
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="K1" s="8">
         <f>+SUMPRODUCT($J$6:$J$1048576,K6:K1048576)</f>
-        <v>890000</v>
+        <v>1052000</v>
       </c>
       <c r="L1" s="8">
         <f>+SUMPRODUCT($J$6:$J$1048576,L6:L1048576)</f>
-        <v>4585000</v>
+        <v>9935000</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1792,7 +1828,7 @@
         <v>24</v>
       </c>
       <c r="J21" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" s="8">
         <v>36000</v>
@@ -1827,7 +1863,7 @@
         <v>24</v>
       </c>
       <c r="J22" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="8">
         <v>36000</v>
@@ -1862,7 +1898,7 @@
         <v>24</v>
       </c>
       <c r="J23" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="8">
         <v>36000</v>
@@ -2010,7 +2046,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>49</v>
@@ -2042,7 +2078,7 @@
         <v>25</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>49</v>
@@ -2071,7 +2107,7 @@
         <v>25</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>49</v>
@@ -2103,7 +2139,7 @@
         <v>25</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>49</v>
@@ -2132,7 +2168,7 @@
         <v>25</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>49</v>
@@ -2488,100 +2524,1251 @@
       <c r="A44" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="C44" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J44" s="8">
+        <v>2</v>
+      </c>
+      <c r="L44" s="8">
+        <v>110000</v>
+      </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="C45" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J45" s="8">
+        <v>1</v>
+      </c>
+      <c r="L45" s="8">
+        <v>110000</v>
+      </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="C46" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J46" s="8">
+        <v>1</v>
+      </c>
+      <c r="L46" s="8">
+        <v>110000</v>
+      </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="C47" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" s="8">
+        <v>1</v>
+      </c>
+      <c r="L47" s="8">
+        <v>110000</v>
+      </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C48" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J48" s="8">
+        <v>3</v>
+      </c>
+      <c r="L48" s="8">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C49" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J49" s="8">
+        <v>3</v>
+      </c>
+      <c r="L49" s="8">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C50" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J50" s="8">
+        <v>1</v>
+      </c>
+      <c r="L50" s="8">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C51" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J51" s="8">
+        <v>1</v>
+      </c>
+      <c r="L51" s="8">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C52" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J52" s="8">
+        <v>1</v>
+      </c>
+      <c r="L52" s="8">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C53" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J53" s="8">
+        <v>1</v>
+      </c>
+      <c r="L53" s="8">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C54" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J54" s="8">
+        <v>1</v>
+      </c>
+      <c r="L54" s="8">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J55" s="8">
+        <v>1</v>
+      </c>
+      <c r="L55" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J56" s="8">
+        <v>2</v>
+      </c>
+      <c r="L56" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J57" s="8">
+        <v>1</v>
+      </c>
+      <c r="L57" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J58" s="8">
+        <v>1</v>
+      </c>
+      <c r="L58" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J59" s="8">
+        <v>1</v>
+      </c>
+      <c r="L59" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C60" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J60" s="8">
+        <v>2</v>
+      </c>
+      <c r="L60" s="8">
+        <v>75000</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C61" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J61" s="8">
+        <v>1</v>
+      </c>
+      <c r="L61" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C62" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J62" s="8">
+        <v>1</v>
+      </c>
+      <c r="L62" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>25</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J63" s="8">
+        <v>1</v>
+      </c>
+      <c r="L63" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J64" s="8">
+        <v>1</v>
+      </c>
+      <c r="L64" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J65" s="8">
+        <v>1</v>
+      </c>
+      <c r="L65" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J66" s="8">
+        <v>1</v>
+      </c>
+      <c r="L66" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J67" s="8">
+        <v>1</v>
+      </c>
+      <c r="K67" s="8">
+        <v>54000</v>
+      </c>
+      <c r="L67" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J68" s="8">
+        <v>1</v>
+      </c>
+      <c r="L68" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J69" s="8">
+        <v>1</v>
+      </c>
+      <c r="L69" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J70" s="8">
+        <v>1</v>
+      </c>
+      <c r="L70" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J71" s="8">
+        <v>1</v>
+      </c>
+      <c r="L71" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J72" s="8">
+        <v>1</v>
+      </c>
+      <c r="L72" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J73" s="8">
+        <v>1</v>
+      </c>
+      <c r="L73" s="8">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J74" s="8">
+        <v>1</v>
+      </c>
+      <c r="L74" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J75" s="8">
+        <v>1</v>
+      </c>
+      <c r="L75" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J76" s="8">
+        <v>1</v>
+      </c>
+      <c r="L76" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J77" s="8">
+        <v>1</v>
+      </c>
+      <c r="L77" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J78" s="8">
+        <v>1</v>
+      </c>
+      <c r="L78" s="8">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J79" s="8">
+        <v>1</v>
+      </c>
+      <c r="L79" s="8">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J80" s="8">
+        <v>1</v>
+      </c>
+      <c r="L80" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J81" s="8">
+        <v>1</v>
+      </c>
+      <c r="L81" s="8">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J82" s="8">
+        <v>1</v>
+      </c>
+      <c r="L82" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J83" s="8">
+        <v>1</v>
+      </c>
+      <c r="L83" s="8">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J84" s="8">
+        <v>1</v>
+      </c>
+      <c r="L84" s="8">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J85" s="8">
+        <v>1</v>
+      </c>
+      <c r="L85" s="8">
+        <v>90000</v>
       </c>
     </row>
   </sheetData>

--- a/docs/referencia/inventario-fisico-template.xlsx
+++ b/docs/referencia/inventario-fisico-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\Negocios\ORVANN\orvann-gestion\docs\referencia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98942CD-A6B2-40F9-AD52-138F6841EAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5749844-3A68-4796-972F-8189EE7E025E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="84">
   <si>
     <t>Tipo</t>
   </si>
@@ -73,27 +73,15 @@
     <t>Fragancia</t>
   </si>
   <si>
-    <t>Loción Versace 100ml</t>
-  </si>
-  <si>
     <t>Pulp Fiction</t>
   </si>
   <si>
-    <t>Estampada espalda completo y bordada frente</t>
-  </si>
-  <si>
     <t>Accesorio</t>
   </si>
   <si>
-    <t>Candela gasolina 100gr</t>
-  </si>
-  <si>
     <t>Dorada</t>
   </si>
   <si>
-    <t>ejemplo</t>
-  </si>
-  <si>
     <t>Estampado Punto Corazón</t>
   </si>
   <si>
@@ -127,18 +115,12 @@
     <t>M</t>
   </si>
   <si>
-    <t>Chompa básica</t>
-  </si>
-  <si>
     <t>XXL</t>
   </si>
   <si>
     <t>L</t>
   </si>
   <si>
-    <t>Básico</t>
-  </si>
-  <si>
     <t>Perla</t>
   </si>
   <si>
@@ -221,6 +203,87 @@
   </si>
   <si>
     <t>Diomedez</t>
+  </si>
+  <si>
+    <t>Reserva</t>
+  </si>
+  <si>
+    <t>Azul</t>
+  </si>
+  <si>
+    <t>220 gr - Garantía</t>
+  </si>
+  <si>
+    <t>Garantía</t>
+  </si>
+  <si>
+    <t>Malas condiciones</t>
+  </si>
+  <si>
+    <t>Mostaza/Negro</t>
+  </si>
+  <si>
+    <t>Rascador Mediano</t>
+  </si>
+  <si>
+    <t>Rosa</t>
+  </si>
+  <si>
+    <t>Rascador Galleta</t>
+  </si>
+  <si>
+    <t>Amarillo</t>
+  </si>
+  <si>
+    <t>Candela</t>
+  </si>
+  <si>
+    <t>Rascador Metal Relieve</t>
+  </si>
+  <si>
+    <t>Rascador Metal 4cm</t>
+  </si>
+  <si>
+    <t>Rascador Metal 6cm</t>
+  </si>
+  <si>
+    <t>Candela Soplete Baraja</t>
+  </si>
+  <si>
+    <t>Candela Tipo Cigarrilos</t>
+  </si>
+  <si>
+    <t>Navaja Grande</t>
+  </si>
+  <si>
+    <t>Navaja Automatica</t>
+  </si>
+  <si>
+    <t>Consumible</t>
+  </si>
+  <si>
+    <t>Vaporizador Orion</t>
+  </si>
+  <si>
+    <t>Vaporizador Singa</t>
+  </si>
+  <si>
+    <t>Vaporizador Pync</t>
+  </si>
+  <si>
+    <t>Eros 100mg</t>
+  </si>
+  <si>
+    <t>2/2 HM 3.4</t>
+  </si>
+  <si>
+    <t>Lacoste Blanca</t>
+  </si>
+  <si>
+    <t>Yara Elixir</t>
+  </si>
+  <si>
+    <t>Yara</t>
   </si>
 </sst>
 </file>
@@ -375,7 +438,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -558,12 +621,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF356854"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -753,15 +810,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -770,9 +824,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="18" fillId="33" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1155,10 +1206,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P85"/>
+  <dimension ref="A1:P151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.5546875" style="2" bestFit="1" customWidth="1"/>
@@ -1167,25 +1218,25 @@
     <col min="7" max="7" width="24.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.21875" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5546875" style="6" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="41.6640625" style="2" customWidth="1"/>
     <col min="14" max="14" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J1" s="8">
-        <f>+SUM(J6:J1048576)</f>
-        <v>98</v>
-      </c>
-      <c r="K1" s="8">
-        <f>+SUMPRODUCT($J$6:$J$1048576,K6:K1048576)</f>
-        <v>1052000</v>
-      </c>
-      <c r="L1" s="8">
-        <f>+SUMPRODUCT($J$6:$J$1048576,L6:L1048576)</f>
-        <v>9935000</v>
+      <c r="J1" s="6">
+        <f>+SUM(J3:J1048576)</f>
+        <v>208</v>
+      </c>
+      <c r="K1" s="6">
+        <f>+SUMPRODUCT($J$3:$J$1048576,K3:K1048576)</f>
+        <v>2783000</v>
+      </c>
+      <c r="L1" s="6">
+        <f>+SUMPRODUCT($J$3:$J$1048576,L3:L1048576)</f>
+        <v>15965000</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1193,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
@@ -1208,255 +1259,246 @@
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="5" t="s">
         <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="4">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="5">
-        <v>46133</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="G3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="6">
+        <v>2</v>
+      </c>
+      <c r="K3" s="6">
+        <v>90000</v>
+      </c>
+      <c r="L3" s="6">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="E4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="6">
+        <v>1</v>
+      </c>
+      <c r="L4" s="6">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="7">
-        <v>3</v>
-      </c>
-      <c r="K3" s="7">
-        <v>49000</v>
-      </c>
-      <c r="L3" s="7">
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="6">
+        <v>2</v>
+      </c>
+      <c r="L5" s="6">
         <v>120000</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="7">
-        <v>4</v>
-      </c>
-      <c r="K4" s="7">
-        <v>250000</v>
-      </c>
-      <c r="L4" s="7">
-        <v>380000</v>
-      </c>
-      <c r="M4" s="3"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="7">
-        <v>2</v>
-      </c>
-      <c r="K5" s="7">
-        <v>8000</v>
-      </c>
-      <c r="L5" s="7">
-        <v>20000</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="8">
-        <v>2</v>
-      </c>
-      <c r="K6" s="8">
+        <v>20</v>
+      </c>
+      <c r="J6" s="6">
+        <v>3</v>
+      </c>
+      <c r="K6" s="6">
         <v>90000</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="6">
         <v>180000</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="8">
-        <v>1</v>
-      </c>
-      <c r="L7" s="8">
+        <v>20</v>
+      </c>
+      <c r="J7" s="6">
+        <v>1</v>
+      </c>
+      <c r="L7" s="6">
         <v>120000</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="8">
-        <v>2</v>
-      </c>
-      <c r="L8" s="8">
+        <v>19</v>
+      </c>
+      <c r="J8" s="6">
+        <v>1</v>
+      </c>
+      <c r="L8" s="6">
         <v>120000</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="8">
-        <v>1</v>
-      </c>
-      <c r="K9" s="8">
-        <v>90000</v>
-      </c>
-      <c r="L9" s="8">
-        <v>180000</v>
+        <v>20</v>
+      </c>
+      <c r="J9" s="6">
+        <v>1</v>
+      </c>
+      <c r="L9" s="6">
+        <v>120000</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>31</v>
@@ -1464,135 +1506,132 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="G10" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="8">
-        <v>1</v>
-      </c>
-      <c r="L10" s="8">
+        <v>20</v>
+      </c>
+      <c r="J10" s="6">
+        <v>1</v>
+      </c>
+      <c r="L10" s="6">
         <v>120000</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J11" s="8">
-        <v>1</v>
-      </c>
-      <c r="L11" s="8">
+        <v>19</v>
+      </c>
+      <c r="J11" s="6">
+        <v>1</v>
+      </c>
+      <c r="L11" s="6">
         <v>120000</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="8">
-        <v>1</v>
-      </c>
-      <c r="L12" s="8">
+        <v>19</v>
+      </c>
+      <c r="J12" s="6">
+        <v>1</v>
+      </c>
+      <c r="L12" s="6">
         <v>120000</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="8">
-        <v>1</v>
-      </c>
-      <c r="L13" s="8">
-        <v>120000</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>40</v>
+        <v>20</v>
+      </c>
+      <c r="J13" s="6">
+        <v>2</v>
+      </c>
+      <c r="L13" s="6">
+        <v>75000</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
@@ -1601,2174 +1640,3827 @@
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" s="8">
-        <v>1</v>
-      </c>
-      <c r="L14" s="8">
-        <v>120000</v>
+        <v>20</v>
+      </c>
+      <c r="J14" s="6">
+        <v>2</v>
+      </c>
+      <c r="L14" s="6">
+        <v>75000</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J15" s="8">
-        <v>1</v>
-      </c>
-      <c r="L15" s="8">
-        <v>120000</v>
+        <v>20</v>
+      </c>
+      <c r="J15" s="6">
+        <v>1</v>
+      </c>
+      <c r="L15" s="6">
+        <v>75000</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="8">
-        <v>2</v>
-      </c>
-      <c r="L16" s="8">
+        <v>20</v>
+      </c>
+      <c r="J16" s="6">
+        <v>1</v>
+      </c>
+      <c r="K16" s="6">
+        <v>54000</v>
+      </c>
+      <c r="L16" s="6">
         <v>75000</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="8">
+        <v>20</v>
+      </c>
+      <c r="J17" s="6">
         <v>2</v>
       </c>
-      <c r="L17" s="8">
+      <c r="K17" s="6">
+        <v>54000</v>
+      </c>
+      <c r="L17" s="6">
         <v>75000</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="8">
-        <v>1</v>
-      </c>
-      <c r="L18" s="8">
-        <v>75000</v>
+        <v>20</v>
+      </c>
+      <c r="J18" s="6">
+        <v>2</v>
+      </c>
+      <c r="K18" s="6">
+        <v>36000</v>
+      </c>
+      <c r="L18" s="6">
+        <v>85000</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="8">
-        <v>1</v>
-      </c>
-      <c r="K19" s="8">
-        <v>54000</v>
-      </c>
-      <c r="L19" s="8">
-        <v>75000</v>
+        <v>20</v>
+      </c>
+      <c r="J19" s="6">
+        <v>2</v>
+      </c>
+      <c r="K19" s="6">
+        <v>36000</v>
+      </c>
+      <c r="L19" s="6">
+        <v>85000</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="8">
-        <v>2</v>
-      </c>
-      <c r="K20" s="8">
-        <v>54000</v>
-      </c>
-      <c r="L20" s="8">
-        <v>75000</v>
+        <v>20</v>
+      </c>
+      <c r="J20" s="6">
+        <v>3</v>
+      </c>
+      <c r="K20" s="6">
+        <v>36000</v>
+      </c>
+      <c r="L20" s="6">
+        <v>85000</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="8">
+        <v>20</v>
+      </c>
+      <c r="J21" s="6">
         <v>2</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21" s="6">
         <v>36000</v>
       </c>
-      <c r="L21" s="8">
+      <c r="L21" s="6">
         <v>85000</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="8">
-        <v>2</v>
-      </c>
-      <c r="K22" s="8">
-        <v>36000</v>
-      </c>
-      <c r="L22" s="8">
-        <v>85000</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>46</v>
+        <v>20</v>
+      </c>
+      <c r="J22" s="6">
+        <v>1</v>
+      </c>
+      <c r="K22" s="6">
+        <v>37000</v>
+      </c>
+      <c r="L22" s="6">
+        <v>75000</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="8">
-        <v>3</v>
-      </c>
-      <c r="K23" s="8">
-        <v>36000</v>
-      </c>
-      <c r="L23" s="8">
-        <v>85000</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>46</v>
+        <v>20</v>
+      </c>
+      <c r="J23" s="6">
+        <v>1</v>
+      </c>
+      <c r="K23" s="6">
+        <v>37000</v>
+      </c>
+      <c r="L23" s="6">
+        <v>75000</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="8">
-        <v>2</v>
-      </c>
-      <c r="K24" s="8">
-        <v>36000</v>
-      </c>
-      <c r="L24" s="8">
-        <v>85000</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>46</v>
+        <v>20</v>
+      </c>
+      <c r="J24" s="6">
+        <v>1</v>
+      </c>
+      <c r="K24" s="6">
+        <v>60000</v>
+      </c>
+      <c r="L24" s="6">
+        <v>75000</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="8">
-        <v>1</v>
-      </c>
-      <c r="K25" s="8">
-        <v>37000</v>
-      </c>
-      <c r="L25" s="8">
-        <v>75000</v>
+        <v>19</v>
+      </c>
+      <c r="J25" s="6">
+        <v>1</v>
+      </c>
+      <c r="L25" s="6">
+        <v>120000</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="8">
-        <v>1</v>
-      </c>
-      <c r="K26" s="8">
-        <v>37000</v>
-      </c>
-      <c r="L26" s="8">
+        <v>20</v>
+      </c>
+      <c r="J26" s="6">
+        <v>1</v>
+      </c>
+      <c r="L26" s="6">
         <v>75000</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="8">
-        <v>1</v>
-      </c>
-      <c r="K27" s="8">
-        <v>60000</v>
-      </c>
-      <c r="L27" s="8">
-        <v>75000</v>
+        <v>19</v>
+      </c>
+      <c r="J27" s="6">
+        <v>1</v>
+      </c>
+      <c r="L27" s="6">
+        <v>120000</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J28" s="8">
-        <v>1</v>
-      </c>
-      <c r="L28" s="8">
-        <v>120000</v>
+        <v>20</v>
+      </c>
+      <c r="J28" s="6">
+        <v>1</v>
+      </c>
+      <c r="L28" s="6">
+        <v>75000</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="8">
-        <v>1</v>
-      </c>
-      <c r="L29" s="8">
-        <v>75000</v>
+        <v>20</v>
+      </c>
+      <c r="J29" s="6">
+        <v>1</v>
+      </c>
+      <c r="L29" s="6">
+        <v>120000</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J30" s="8">
-        <v>1</v>
-      </c>
-      <c r="L30" s="8">
-        <v>120000</v>
+        <v>20</v>
+      </c>
+      <c r="J30" s="6">
+        <v>2</v>
+      </c>
+      <c r="L30" s="6">
+        <v>100000</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J31" s="8">
-        <v>1</v>
-      </c>
-      <c r="L31" s="8">
-        <v>75000</v>
+        <v>20</v>
+      </c>
+      <c r="J31" s="6">
+        <v>1</v>
+      </c>
+      <c r="L31" s="6">
+        <v>100000</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J32" s="8">
-        <v>1</v>
-      </c>
-      <c r="L32" s="8">
-        <v>120000</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>51</v>
+        <v>20</v>
+      </c>
+      <c r="J32" s="6">
+        <v>1</v>
+      </c>
+      <c r="L32" s="6">
+        <v>100000</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J33" s="8">
-        <v>2</v>
-      </c>
-      <c r="L33" s="8">
-        <v>100000</v>
+        <v>20</v>
+      </c>
+      <c r="J33" s="6">
+        <v>1</v>
+      </c>
+      <c r="L33" s="6">
+        <v>90000</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J34" s="8">
-        <v>1</v>
-      </c>
-      <c r="L34" s="8">
-        <v>100000</v>
+        <v>20</v>
+      </c>
+      <c r="J34" s="6">
+        <v>1</v>
+      </c>
+      <c r="L34" s="6">
+        <v>90000</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J35" s="8">
-        <v>1</v>
-      </c>
-      <c r="L35" s="8">
-        <v>100000</v>
+        <v>20</v>
+      </c>
+      <c r="J35" s="6">
+        <v>1</v>
+      </c>
+      <c r="L35" s="6">
+        <v>90000</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J36" s="8">
-        <v>1</v>
-      </c>
-      <c r="L36" s="8">
-        <v>90000</v>
+        <v>20</v>
+      </c>
+      <c r="J36" s="6">
+        <v>1</v>
+      </c>
+      <c r="L36" s="6">
+        <v>100000</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J37" s="8">
-        <v>1</v>
-      </c>
-      <c r="L37" s="8">
-        <v>90000</v>
+        <v>20</v>
+      </c>
+      <c r="J37" s="6">
+        <v>1</v>
+      </c>
+      <c r="L37" s="6">
+        <v>100000</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J38" s="8">
-        <v>1</v>
-      </c>
-      <c r="L38" s="8">
-        <v>90000</v>
+        <v>20</v>
+      </c>
+      <c r="J38" s="6">
+        <v>1</v>
+      </c>
+      <c r="L38" s="6">
+        <v>100000</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J39" s="8">
-        <v>1</v>
-      </c>
-      <c r="L39" s="8">
-        <v>100000</v>
+        <v>20</v>
+      </c>
+      <c r="J39" s="6">
+        <v>1</v>
+      </c>
+      <c r="K39" s="6">
+        <v>54000</v>
+      </c>
+      <c r="L39" s="6">
+        <v>75000</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J40" s="8">
-        <v>1</v>
-      </c>
-      <c r="L40" s="8">
-        <v>100000</v>
+        <v>20</v>
+      </c>
+      <c r="J40" s="6">
+        <v>1</v>
+      </c>
+      <c r="K40" s="6">
+        <v>54000</v>
+      </c>
+      <c r="L40" s="6">
+        <v>75000</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J41" s="8">
-        <v>1</v>
-      </c>
-      <c r="L41" s="8">
-        <v>100000</v>
+        <v>20</v>
+      </c>
+      <c r="J41" s="6">
+        <v>2</v>
+      </c>
+      <c r="L41" s="6">
+        <v>110000</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J42" s="8">
-        <v>1</v>
-      </c>
-      <c r="K42" s="8">
-        <v>54000</v>
-      </c>
-      <c r="L42" s="8">
-        <v>75000</v>
+        <v>20</v>
+      </c>
+      <c r="J42" s="6">
+        <v>1</v>
+      </c>
+      <c r="L42" s="6">
+        <v>110000</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J43" s="8">
-        <v>1</v>
-      </c>
-      <c r="K43" s="8">
-        <v>54000</v>
-      </c>
-      <c r="L43" s="8">
-        <v>75000</v>
+        <v>20</v>
+      </c>
+      <c r="J43" s="6">
+        <v>1</v>
+      </c>
+      <c r="L43" s="6">
+        <v>110000</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J44" s="8">
-        <v>2</v>
-      </c>
-      <c r="L44" s="8">
+        <v>20</v>
+      </c>
+      <c r="J44" s="6">
+        <v>1</v>
+      </c>
+      <c r="L44" s="6">
         <v>110000</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J45" s="8">
-        <v>1</v>
-      </c>
-      <c r="L45" s="8">
+        <v>20</v>
+      </c>
+      <c r="J45" s="6">
+        <v>3</v>
+      </c>
+      <c r="L45" s="6">
         <v>110000</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J46" s="8">
-        <v>1</v>
-      </c>
-      <c r="L46" s="8">
+        <v>20</v>
+      </c>
+      <c r="J46" s="6">
+        <v>3</v>
+      </c>
+      <c r="L46" s="6">
         <v>110000</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J47" s="8">
-        <v>1</v>
-      </c>
-      <c r="L47" s="8">
+        <v>20</v>
+      </c>
+      <c r="J47" s="6">
+        <v>1</v>
+      </c>
+      <c r="L47" s="6">
         <v>110000</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J48" s="8">
-        <v>3</v>
-      </c>
-      <c r="L48" s="8">
+        <v>20</v>
+      </c>
+      <c r="J48" s="6">
+        <v>1</v>
+      </c>
+      <c r="L48" s="6">
         <v>110000</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J49" s="8">
-        <v>3</v>
-      </c>
-      <c r="L49" s="8">
+        <v>20</v>
+      </c>
+      <c r="J49" s="6">
+        <v>1</v>
+      </c>
+      <c r="L49" s="6">
         <v>110000</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J50" s="8">
-        <v>1</v>
-      </c>
-      <c r="L50" s="8">
+        <v>20</v>
+      </c>
+      <c r="J50" s="6">
+        <v>1</v>
+      </c>
+      <c r="L50" s="6">
         <v>110000</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J51" s="8">
-        <v>1</v>
-      </c>
-      <c r="L51" s="8">
+        <v>20</v>
+      </c>
+      <c r="J51" s="6">
+        <v>1</v>
+      </c>
+      <c r="L51" s="6">
         <v>110000</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J52" s="8">
-        <v>1</v>
-      </c>
-      <c r="L52" s="8">
-        <v>110000</v>
+        <v>19</v>
+      </c>
+      <c r="J52" s="6">
+        <v>1</v>
+      </c>
+      <c r="L52" s="6">
+        <v>120000</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J53" s="8">
-        <v>1</v>
-      </c>
-      <c r="L53" s="8">
-        <v>110000</v>
+        <v>19</v>
+      </c>
+      <c r="J53" s="6">
+        <v>2</v>
+      </c>
+      <c r="L53" s="6">
+        <v>120000</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J54" s="8">
-        <v>1</v>
-      </c>
-      <c r="L54" s="8">
-        <v>110000</v>
+        <v>19</v>
+      </c>
+      <c r="J54" s="6">
+        <v>1</v>
+      </c>
+      <c r="L54" s="6">
+        <v>120000</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J55" s="8">
-        <v>1</v>
-      </c>
-      <c r="L55" s="8">
-        <v>120000</v>
+        <v>20</v>
+      </c>
+      <c r="J55" s="6">
+        <v>1</v>
+      </c>
+      <c r="L55" s="6">
+        <v>75000</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J56" s="8">
-        <v>2</v>
-      </c>
-      <c r="L56" s="8">
-        <v>120000</v>
+        <v>20</v>
+      </c>
+      <c r="J56" s="6">
+        <v>1</v>
+      </c>
+      <c r="L56" s="6">
+        <v>75000</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J57" s="8">
-        <v>1</v>
-      </c>
-      <c r="L57" s="8">
-        <v>120000</v>
+        <v>20</v>
+      </c>
+      <c r="J57" s="6">
+        <v>2</v>
+      </c>
+      <c r="L57" s="6">
+        <v>75000</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J58" s="8">
-        <v>1</v>
-      </c>
-      <c r="L58" s="8">
+        <v>20</v>
+      </c>
+      <c r="J58" s="6">
+        <v>1</v>
+      </c>
+      <c r="L58" s="6">
         <v>75000</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J59" s="8">
-        <v>1</v>
-      </c>
-      <c r="L59" s="8">
+        <v>20</v>
+      </c>
+      <c r="J59" s="6">
+        <v>1</v>
+      </c>
+      <c r="L59" s="6">
         <v>75000</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J60" s="8">
-        <v>2</v>
-      </c>
-      <c r="L60" s="8">
+        <v>20</v>
+      </c>
+      <c r="J60" s="6">
+        <v>1</v>
+      </c>
+      <c r="L60" s="6">
         <v>75000</v>
-      </c>
-      <c r="M60" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J61" s="8">
-        <v>1</v>
-      </c>
-      <c r="L61" s="8">
-        <v>75000</v>
+        <v>19</v>
+      </c>
+      <c r="J61" s="6">
+        <v>1</v>
+      </c>
+      <c r="L61" s="6">
+        <v>120000</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J62" s="8">
-        <v>1</v>
-      </c>
-      <c r="L62" s="8">
-        <v>75000</v>
+        <v>19</v>
+      </c>
+      <c r="J62" s="6">
+        <v>1</v>
+      </c>
+      <c r="L62" s="6">
+        <v>120000</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J63" s="8">
-        <v>1</v>
-      </c>
-      <c r="L63" s="8">
-        <v>75000</v>
+        <v>19</v>
+      </c>
+      <c r="J63" s="6">
+        <v>1</v>
+      </c>
+      <c r="L63" s="6">
+        <v>120000</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J64" s="8">
-        <v>1</v>
-      </c>
-      <c r="L64" s="8">
-        <v>120000</v>
+        <v>20</v>
+      </c>
+      <c r="J64" s="6">
+        <v>1</v>
+      </c>
+      <c r="K64" s="6">
+        <v>54000</v>
+      </c>
+      <c r="L64" s="6">
+        <v>75000</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J65" s="8">
-        <v>1</v>
-      </c>
-      <c r="L65" s="8">
+        <v>19</v>
+      </c>
+      <c r="J65" s="6">
+        <v>1</v>
+      </c>
+      <c r="L65" s="6">
         <v>120000</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J66" s="8">
-        <v>1</v>
-      </c>
-      <c r="L66" s="8">
+        <v>19</v>
+      </c>
+      <c r="J66" s="6">
+        <v>1</v>
+      </c>
+      <c r="L66" s="6">
         <v>120000</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J67" s="8">
-        <v>1</v>
-      </c>
-      <c r="K67" s="8">
-        <v>54000</v>
-      </c>
-      <c r="L67" s="8">
-        <v>75000</v>
+        <v>19</v>
+      </c>
+      <c r="J67" s="6">
+        <v>1</v>
+      </c>
+      <c r="L67" s="6">
+        <v>120000</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J68" s="8">
-        <v>1</v>
-      </c>
-      <c r="L68" s="8">
+        <v>20</v>
+      </c>
+      <c r="J68" s="6">
+        <v>1</v>
+      </c>
+      <c r="L68" s="6">
         <v>120000</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J69" s="8">
-        <v>1</v>
-      </c>
-      <c r="L69" s="8">
+        <v>20</v>
+      </c>
+      <c r="J69" s="6">
+        <v>1</v>
+      </c>
+      <c r="L69" s="6">
         <v>120000</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J70" s="8">
-        <v>1</v>
-      </c>
-      <c r="L70" s="8">
-        <v>120000</v>
+        <v>20</v>
+      </c>
+      <c r="J70" s="6">
+        <v>1</v>
+      </c>
+      <c r="L70" s="6">
+        <v>100000</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J71" s="8">
-        <v>1</v>
-      </c>
-      <c r="L71" s="8">
+        <v>20</v>
+      </c>
+      <c r="J71" s="6">
+        <v>1</v>
+      </c>
+      <c r="L71" s="6">
         <v>120000</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C72" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="G72" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J72" s="8">
-        <v>1</v>
-      </c>
-      <c r="L72" s="8">
+        <v>20</v>
+      </c>
+      <c r="J72" s="6">
+        <v>1</v>
+      </c>
+      <c r="L72" s="6">
         <v>120000</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J73" s="8">
-        <v>1</v>
-      </c>
-      <c r="L73" s="8">
-        <v>100000</v>
+        <v>20</v>
+      </c>
+      <c r="J73" s="6">
+        <v>1</v>
+      </c>
+      <c r="L73" s="6">
+        <v>75000</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J74" s="8">
-        <v>1</v>
-      </c>
-      <c r="L74" s="8">
-        <v>120000</v>
+        <v>20</v>
+      </c>
+      <c r="J74" s="6">
+        <v>1</v>
+      </c>
+      <c r="L74" s="6">
+        <v>75000</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C75" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D75" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="G75" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J75" s="8">
-        <v>1</v>
-      </c>
-      <c r="L75" s="8">
-        <v>120000</v>
+        <v>20</v>
+      </c>
+      <c r="J75" s="6">
+        <v>1</v>
+      </c>
+      <c r="L75" s="6">
+        <v>90000</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J76" s="8">
-        <v>1</v>
-      </c>
-      <c r="L76" s="8">
+        <v>20</v>
+      </c>
+      <c r="J76" s="6">
+        <v>1</v>
+      </c>
+      <c r="L76" s="6">
         <v>75000</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J77" s="8">
-        <v>1</v>
-      </c>
-      <c r="L77" s="8">
-        <v>75000</v>
+        <v>20</v>
+      </c>
+      <c r="J77" s="6">
+        <v>1</v>
+      </c>
+      <c r="L77" s="6">
+        <v>120000</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J78" s="8">
-        <v>1</v>
-      </c>
-      <c r="L78" s="8">
-        <v>90000</v>
+        <v>20</v>
+      </c>
+      <c r="J78" s="6">
+        <v>1</v>
+      </c>
+      <c r="L78" s="6">
+        <v>100000</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J79" s="8">
-        <v>1</v>
-      </c>
-      <c r="L79" s="8">
-        <v>75000</v>
+        <v>20</v>
+      </c>
+      <c r="J79" s="6">
+        <v>1</v>
+      </c>
+      <c r="L79" s="6">
+        <v>120000</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J80" s="6">
+        <v>1</v>
+      </c>
+      <c r="L80" s="6">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J80" s="8">
-        <v>1</v>
-      </c>
-      <c r="L80" s="8">
-        <v>120000</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D81" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J81" s="6">
+        <v>1</v>
+      </c>
+      <c r="L81" s="6">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J82" s="6">
+        <v>1</v>
+      </c>
+      <c r="L82" s="6">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J83" s="6">
+        <v>1</v>
+      </c>
+      <c r="L83" s="6">
+        <v>120000</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J84" s="6">
+        <v>1</v>
+      </c>
+      <c r="L84" s="6">
+        <v>75000</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J85" s="6">
+        <v>1</v>
+      </c>
+      <c r="L85" s="6">
+        <v>110000</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J86" s="6">
+        <v>1</v>
+      </c>
+      <c r="L86" s="6">
+        <v>110000</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J87" s="6">
+        <v>1</v>
+      </c>
+      <c r="L87" s="6">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J88" s="6">
+        <v>1</v>
+      </c>
+      <c r="L88" s="6">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J89" s="6">
+        <v>1</v>
+      </c>
+      <c r="L89" s="6">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J90" s="6">
+        <v>1</v>
+      </c>
+      <c r="L90" s="6">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J91" s="6">
+        <v>1</v>
+      </c>
+      <c r="L91" s="6">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J92" s="6">
+        <v>1</v>
+      </c>
+      <c r="L92" s="6">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J93" s="6">
+        <v>1</v>
+      </c>
+      <c r="L93" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J94" s="6">
+        <v>1</v>
+      </c>
+      <c r="L94" s="6">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J95" s="6">
+        <v>1</v>
+      </c>
+      <c r="L95" s="6">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J96" s="6">
+        <v>1</v>
+      </c>
+      <c r="L96" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J97" s="6">
+        <v>1</v>
+      </c>
+      <c r="L97" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J98" s="6">
+        <v>1</v>
+      </c>
+      <c r="L98" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J99" s="6">
+        <v>1</v>
+      </c>
+      <c r="L99" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J100" s="6">
+        <v>1</v>
+      </c>
+      <c r="L100" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J101" s="6">
+        <v>1</v>
+      </c>
+      <c r="L101" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J102" s="6">
+        <v>1</v>
+      </c>
+      <c r="L102" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J103" s="6">
+        <v>1</v>
+      </c>
+      <c r="L103" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J104" s="6">
+        <v>1</v>
+      </c>
+      <c r="L104" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J105" s="6">
+        <v>1</v>
+      </c>
+      <c r="L105" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J106" s="6">
+        <v>1</v>
+      </c>
+      <c r="L106" s="6">
+        <v>120000</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J107" s="6">
+        <v>1</v>
+      </c>
+      <c r="L107" s="6">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J108" s="6">
+        <v>4</v>
+      </c>
+      <c r="L108" s="6">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J109" s="6">
+        <v>2</v>
+      </c>
+      <c r="L109" s="6">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J110" s="6">
+        <v>1</v>
+      </c>
+      <c r="L110" s="6">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J111" s="6">
+        <v>1</v>
+      </c>
+      <c r="L111" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J112" s="6">
+        <v>1</v>
+      </c>
+      <c r="L112" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C113" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H81" s="2" t="s">
+      <c r="D113" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J113" s="6">
+        <v>1</v>
+      </c>
+      <c r="L113" s="6">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J114" s="6">
+        <v>1</v>
+      </c>
+      <c r="L114" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J115" s="6">
+        <v>1</v>
+      </c>
+      <c r="L115" s="6">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J116" s="6">
+        <v>1</v>
+      </c>
+      <c r="L116" s="6">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J117" s="6">
+        <v>2</v>
+      </c>
+      <c r="L117" s="6">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J118" s="6">
+        <v>2</v>
+      </c>
+      <c r="L118" s="6">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J119" s="6">
+        <v>1</v>
+      </c>
+      <c r="L119" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J120" s="6">
+        <v>1</v>
+      </c>
+      <c r="L120" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J121" s="6">
+        <v>1</v>
+      </c>
+      <c r="L121" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J122" s="6">
+        <v>3</v>
+      </c>
+      <c r="L122" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J123" s="6">
+        <v>2</v>
+      </c>
+      <c r="L123" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J124" s="6">
+        <v>1</v>
+      </c>
+      <c r="L124" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I81" s="2" t="s">
+      <c r="D125" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J125" s="6">
+        <v>2</v>
+      </c>
+      <c r="L125" s="6">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J81" s="8">
-        <v>1</v>
-      </c>
-      <c r="L81" s="8">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D82" s="2" t="s">
+      <c r="D126" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E82" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J82" s="8">
-        <v>1</v>
-      </c>
-      <c r="L82" s="8">
+      <c r="E126" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J126" s="6">
+        <v>1</v>
+      </c>
+      <c r="L126" s="6">
         <v>120000</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J83" s="8">
-        <v>1</v>
-      </c>
-      <c r="L83" s="8">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C84" s="2" t="s">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D84" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J84" s="8">
-        <v>1</v>
-      </c>
-      <c r="L84" s="8">
+      <c r="G127" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J127" s="6">
+        <v>1</v>
+      </c>
+      <c r="L127" s="6">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J128" s="6">
+        <v>1</v>
+      </c>
+      <c r="L128" s="6">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J129" s="6">
+        <v>1</v>
+      </c>
+      <c r="L129" s="6">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J130" s="6">
+        <v>1</v>
+      </c>
+      <c r="L130" s="6">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J131" s="6">
+        <v>1</v>
+      </c>
+      <c r="L131" s="6">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J132" s="6">
+        <v>1</v>
+      </c>
+      <c r="L132" s="6">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J133" s="6">
+        <v>2</v>
+      </c>
+      <c r="K133" s="6">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J134" s="6">
+        <v>2</v>
+      </c>
+      <c r="K134" s="6">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J135" s="6">
+        <v>1</v>
+      </c>
+      <c r="K135" s="6">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J136" s="6">
+        <v>4</v>
+      </c>
+      <c r="K136" s="6">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A137" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J137" s="6">
+        <v>3</v>
+      </c>
+      <c r="K137" s="6">
+        <v>19500</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J138" s="6">
+        <v>1</v>
+      </c>
+      <c r="K138" s="6">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A139" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J139" s="6">
+        <v>1</v>
+      </c>
+      <c r="K139" s="6">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J140" s="6">
+        <v>1</v>
+      </c>
+      <c r="K140" s="6">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J141" s="6">
+        <v>1</v>
+      </c>
+      <c r="K141" s="6">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J142" s="6">
+        <v>1</v>
+      </c>
+      <c r="K142" s="6">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A143" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J143" s="6">
+        <v>1</v>
+      </c>
+      <c r="K143" s="6">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J144" s="6">
+        <v>10</v>
+      </c>
+      <c r="K144" s="6">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A145" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J145" s="6">
+        <v>10</v>
+      </c>
+      <c r="K145" s="6">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J146" s="6">
+        <v>5</v>
+      </c>
+      <c r="K146" s="6">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A147" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="J147" s="6">
+        <v>1</v>
+      </c>
+      <c r="K147" s="6">
+        <v>255000</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A148" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J148" s="6">
+        <v>1</v>
+      </c>
+      <c r="K148" s="6">
+        <v>320000</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A149" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J149" s="6">
+        <v>1</v>
+      </c>
+      <c r="K149" s="6">
+        <v>220000</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J150" s="6">
+        <v>1</v>
+      </c>
+      <c r="K150" s="6">
+        <v>230000</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A151" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J151" s="6">
+        <v>1</v>
+      </c>
+      <c r="K151" s="6">
         <v>120000</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I85" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J85" s="8">
-        <v>1</v>
-      </c>
-      <c r="L85" s="8">
-        <v>90000</v>
       </c>
     </row>
   </sheetData>
